--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200486</v>
+        <v>121200479</v>
       </c>
       <c r="B81" t="n">
-        <v>90153</v>
+        <v>91965</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9642,21 +9642,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3286</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471358</v>
+        <v>471412</v>
       </c>
       <c r="R81" t="n">
-        <v>7015668</v>
+        <v>7015570</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9728,10 +9728,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200484</v>
+        <v>121200478</v>
       </c>
       <c r="B82" t="n">
-        <v>91994</v>
+        <v>86285</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,21 +9744,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1968</v>
+        <v>3739</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471377</v>
+        <v>471414</v>
       </c>
       <c r="R82" t="n">
-        <v>7015535</v>
+        <v>7015573</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9812,6 +9812,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9830,10 +9831,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121200501</v>
+        <v>121200483</v>
       </c>
       <c r="B83" t="n">
-        <v>100337</v>
+        <v>90242</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9842,38 +9843,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>5754</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471381</v>
+        <v>471417</v>
       </c>
       <c r="R83" t="n">
-        <v>7015432</v>
+        <v>7015526</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9900,12 +9901,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9932,10 +9933,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121200479</v>
+        <v>121200500</v>
       </c>
       <c r="B84" t="n">
-        <v>91955</v>
+        <v>90697</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9948,34 +9949,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471412</v>
+        <v>471425</v>
       </c>
       <c r="R84" t="n">
-        <v>7015570</v>
+        <v>7015607</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10002,12 +10003,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10034,10 +10035,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200485</v>
+        <v>121200466</v>
       </c>
       <c r="B85" t="n">
-        <v>91994</v>
+        <v>88541</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10050,21 +10051,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10074,10 +10075,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471415</v>
+        <v>471438</v>
       </c>
       <c r="R85" t="n">
-        <v>7015546</v>
+        <v>7015583</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10136,10 +10137,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200478</v>
+        <v>121200485</v>
       </c>
       <c r="B86" t="n">
-        <v>86279</v>
+        <v>92004</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10152,21 +10153,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3739</v>
+        <v>1968</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10176,10 +10177,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471414</v>
+        <v>471415</v>
       </c>
       <c r="R86" t="n">
-        <v>7015573</v>
+        <v>7015546</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10220,7 +10221,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10239,10 +10239,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200480</v>
+        <v>121200486</v>
       </c>
       <c r="B87" t="n">
-        <v>91955</v>
+        <v>90163</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10255,21 +10255,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4361</v>
+        <v>3286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471415</v>
+        <v>471358</v>
       </c>
       <c r="R87" t="n">
-        <v>7015552</v>
+        <v>7015668</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10341,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121200475</v>
+        <v>121200501</v>
       </c>
       <c r="B88" t="n">
-        <v>91620</v>
+        <v>100347</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10357,34 +10357,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471431</v>
+        <v>471381</v>
       </c>
       <c r="R88" t="n">
-        <v>7015638</v>
+        <v>7015432</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10443,10 +10443,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200466</v>
+        <v>121200475</v>
       </c>
       <c r="B89" t="n">
-        <v>88535</v>
+        <v>91630</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10455,25 +10455,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4412</v>
+        <v>4769</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,10 +10483,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471438</v>
+        <v>471431</v>
       </c>
       <c r="R89" t="n">
-        <v>7015583</v>
+        <v>7015638</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10545,10 +10545,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200483</v>
+        <v>121200480</v>
       </c>
       <c r="B90" t="n">
-        <v>90232</v>
+        <v>91965</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10561,21 +10561,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471417</v>
+        <v>471415</v>
       </c>
       <c r="R90" t="n">
-        <v>7015526</v>
+        <v>7015552</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10647,10 +10647,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200474</v>
+        <v>121200484</v>
       </c>
       <c r="B91" t="n">
-        <v>90211</v>
+        <v>92004</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10663,21 +10663,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5733</v>
+        <v>1968</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471420</v>
+        <v>471377</v>
       </c>
       <c r="R91" t="n">
-        <v>7015545</v>
+        <v>7015535</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10731,7 +10731,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10750,10 +10749,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121200500</v>
+        <v>121200474</v>
       </c>
       <c r="B92" t="n">
-        <v>90687</v>
+        <v>90221</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10766,34 +10765,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>5733</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471425</v>
+        <v>471420</v>
       </c>
       <c r="R92" t="n">
-        <v>7015607</v>
+        <v>7015545</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10820,12 +10819,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10834,6 +10833,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259416</v>
+        <v>121259347</v>
       </c>
       <c r="B93" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,27 +10868,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10896,10 +10895,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471606</v>
+        <v>471434</v>
       </c>
       <c r="R93" t="n">
-        <v>7015715</v>
+        <v>7015412</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10926,17 +10925,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10945,6 +10939,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10963,10 +10958,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259347</v>
+        <v>121259416</v>
       </c>
       <c r="B94" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10979,26 +10974,27 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11006,10 +11002,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471434</v>
+        <v>471606</v>
       </c>
       <c r="R94" t="n">
-        <v>7015412</v>
+        <v>7015715</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11036,12 +11032,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11050,7 +11051,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>121259365</v>
       </c>
       <c r="B95" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307817</v>
+        <v>121307814</v>
       </c>
       <c r="B96" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,34 +11191,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471626</v>
+        <v>471233</v>
       </c>
       <c r="R96" t="n">
-        <v>7015589</v>
+        <v>7015703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11251,6 +11259,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11277,10 +11290,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307814</v>
+        <v>121307817</v>
       </c>
       <c r="B97" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11293,42 +11306,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471233</v>
+        <v>471626</v>
       </c>
       <c r="R97" t="n">
-        <v>7015703</v>
+        <v>7015589</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11361,11 +11366,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11392,10 +11392,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307813</v>
+        <v>121307815</v>
       </c>
       <c r="B98" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11408,34 +11408,50 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471632</v>
+        <v>471653</v>
       </c>
       <c r="R98" t="n">
-        <v>7015584</v>
+        <v>7015676</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11468,6 +11484,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11494,10 +11515,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307815</v>
+        <v>121307816</v>
       </c>
       <c r="B99" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11510,50 +11531,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471653</v>
+        <v>471234</v>
       </c>
       <c r="R99" t="n">
-        <v>7015676</v>
+        <v>7015703</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11586,11 +11591,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11617,10 +11617,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307816</v>
+        <v>121307813</v>
       </c>
       <c r="B100" t="n">
-        <v>90705</v>
+        <v>90697</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471234</v>
+        <v>471632</v>
       </c>
       <c r="R100" t="n">
-        <v>7015703</v>
+        <v>7015584</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200479</v>
+        <v>121200478</v>
       </c>
       <c r="B81" t="n">
-        <v>91965</v>
+        <v>86285</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9642,21 +9642,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>3739</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471412</v>
+        <v>471414</v>
       </c>
       <c r="R81" t="n">
-        <v>7015570</v>
+        <v>7015573</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9710,6 +9710,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9728,10 +9729,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200478</v>
+        <v>121200500</v>
       </c>
       <c r="B82" t="n">
-        <v>86285</v>
+        <v>90697</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,34 +9745,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3739</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471414</v>
+        <v>471425</v>
       </c>
       <c r="R82" t="n">
-        <v>7015573</v>
+        <v>7015607</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9798,12 +9799,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9812,7 +9813,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9933,10 +9933,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121200500</v>
+        <v>121200474</v>
       </c>
       <c r="B84" t="n">
-        <v>90697</v>
+        <v>90221</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9949,34 +9949,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>5733</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471425</v>
+        <v>471420</v>
       </c>
       <c r="R84" t="n">
-        <v>7015607</v>
+        <v>7015545</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10003,12 +10003,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10017,6 +10017,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10035,10 +10036,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200466</v>
+        <v>121200480</v>
       </c>
       <c r="B85" t="n">
-        <v>88541</v>
+        <v>91965</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10051,21 +10052,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4412</v>
+        <v>4361</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10075,10 +10076,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471438</v>
+        <v>471415</v>
       </c>
       <c r="R85" t="n">
-        <v>7015583</v>
+        <v>7015552</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10137,10 +10138,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200485</v>
+        <v>121200479</v>
       </c>
       <c r="B86" t="n">
-        <v>92004</v>
+        <v>91965</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10153,21 +10154,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10177,10 +10178,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471415</v>
+        <v>471412</v>
       </c>
       <c r="R86" t="n">
-        <v>7015546</v>
+        <v>7015570</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10239,10 +10240,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200486</v>
+        <v>121200475</v>
       </c>
       <c r="B87" t="n">
-        <v>90163</v>
+        <v>91630</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10251,25 +10252,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3286</v>
+        <v>4769</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10279,10 +10280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471358</v>
+        <v>471431</v>
       </c>
       <c r="R87" t="n">
-        <v>7015668</v>
+        <v>7015638</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10341,10 +10342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121200501</v>
+        <v>121200484</v>
       </c>
       <c r="B88" t="n">
-        <v>100347</v>
+        <v>92004</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10353,38 +10354,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>1968</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471381</v>
+        <v>471377</v>
       </c>
       <c r="R88" t="n">
-        <v>7015432</v>
+        <v>7015535</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10411,12 +10412,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10443,10 +10444,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200475</v>
+        <v>121200501</v>
       </c>
       <c r="B89" t="n">
-        <v>91630</v>
+        <v>100347</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10459,34 +10460,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471431</v>
+        <v>471381</v>
       </c>
       <c r="R89" t="n">
-        <v>7015638</v>
+        <v>7015432</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10513,12 +10514,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10545,10 +10546,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200480</v>
+        <v>121200485</v>
       </c>
       <c r="B90" t="n">
-        <v>91965</v>
+        <v>92004</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10561,21 +10562,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>1968</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10588,7 +10589,7 @@
         <v>471415</v>
       </c>
       <c r="R90" t="n">
-        <v>7015552</v>
+        <v>7015546</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10647,10 +10648,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200484</v>
+        <v>121200466</v>
       </c>
       <c r="B91" t="n">
-        <v>92004</v>
+        <v>88541</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10663,21 +10664,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10687,10 +10688,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471377</v>
+        <v>471438</v>
       </c>
       <c r="R91" t="n">
-        <v>7015535</v>
+        <v>7015583</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10749,10 +10750,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121200474</v>
+        <v>121200486</v>
       </c>
       <c r="B92" t="n">
-        <v>90221</v>
+        <v>90163</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10765,21 +10766,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5733</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10789,10 +10790,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471420</v>
+        <v>471358</v>
       </c>
       <c r="R92" t="n">
-        <v>7015545</v>
+        <v>7015668</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10833,7 +10834,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259347</v>
+        <v>121259416</v>
       </c>
       <c r="B93" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,26 +10868,27 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10895,10 +10896,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471434</v>
+        <v>471606</v>
       </c>
       <c r="R93" t="n">
-        <v>7015412</v>
+        <v>7015715</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10925,12 +10926,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10939,7 +10945,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10958,10 +10963,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259416</v>
+        <v>121259347</v>
       </c>
       <c r="B94" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10974,27 +10979,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11002,10 +11006,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471606</v>
+        <v>471434</v>
       </c>
       <c r="R94" t="n">
-        <v>7015715</v>
+        <v>7015412</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11032,17 +11036,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11051,6 +11050,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307814</v>
+        <v>121307816</v>
       </c>
       <c r="B96" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,39 +11191,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471233</v>
+        <v>471234</v>
       </c>
       <c r="R96" t="n">
         <v>7015703</v>
@@ -11259,11 +11251,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11290,10 +11277,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307817</v>
+        <v>121307813</v>
       </c>
       <c r="B97" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11306,21 +11293,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11330,10 +11317,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471626</v>
+        <v>471632</v>
       </c>
       <c r="R97" t="n">
-        <v>7015589</v>
+        <v>7015584</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11392,10 +11379,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307815</v>
+        <v>121307817</v>
       </c>
       <c r="B98" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11408,50 +11395,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471653</v>
+        <v>471626</v>
       </c>
       <c r="R98" t="n">
-        <v>7015676</v>
+        <v>7015589</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11484,11 +11455,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11515,10 +11481,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307816</v>
+        <v>121307814</v>
       </c>
       <c r="B99" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11531,31 +11497,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471234</v>
+        <v>471233</v>
       </c>
       <c r="R99" t="n">
         <v>7015703</v>
@@ -11591,6 +11565,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11617,10 +11596,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307813</v>
+        <v>121307815</v>
       </c>
       <c r="B100" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11633,34 +11612,50 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471632</v>
+        <v>471653</v>
       </c>
       <c r="R100" t="n">
-        <v>7015584</v>
+        <v>7015676</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11693,6 +11688,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200478</v>
+        <v>121200475</v>
       </c>
       <c r="B81" t="n">
-        <v>86285</v>
+        <v>91642</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9638,25 +9638,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3739</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471414</v>
+        <v>471431</v>
       </c>
       <c r="R81" t="n">
-        <v>7015573</v>
+        <v>7015638</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9710,7 +9710,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9729,10 +9728,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200500</v>
+        <v>121200480</v>
       </c>
       <c r="B82" t="n">
-        <v>90697</v>
+        <v>91977</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9745,34 +9744,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471425</v>
+        <v>471415</v>
       </c>
       <c r="R82" t="n">
-        <v>7015607</v>
+        <v>7015552</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9799,12 +9798,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9834,7 +9833,7 @@
         <v>121200483</v>
       </c>
       <c r="B83" t="n">
-        <v>90242</v>
+        <v>90254</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9933,10 +9932,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121200474</v>
+        <v>121200501</v>
       </c>
       <c r="B84" t="n">
-        <v>90221</v>
+        <v>100360</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9945,38 +9944,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5733</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471420</v>
+        <v>471381</v>
       </c>
       <c r="R84" t="n">
-        <v>7015545</v>
+        <v>7015432</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10003,12 +10002,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10017,7 +10016,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10036,10 +10034,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200480</v>
+        <v>121200478</v>
       </c>
       <c r="B85" t="n">
-        <v>91965</v>
+        <v>86291</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10052,21 +10050,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4361</v>
+        <v>3739</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10076,10 +10074,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471415</v>
+        <v>471414</v>
       </c>
       <c r="R85" t="n">
-        <v>7015552</v>
+        <v>7015573</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10120,6 +10118,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10138,10 +10137,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200479</v>
+        <v>121200484</v>
       </c>
       <c r="B86" t="n">
-        <v>91965</v>
+        <v>92016</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10154,21 +10153,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>1968</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10178,10 +10177,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471412</v>
+        <v>471377</v>
       </c>
       <c r="R86" t="n">
-        <v>7015570</v>
+        <v>7015535</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10240,10 +10239,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200475</v>
+        <v>121200474</v>
       </c>
       <c r="B87" t="n">
-        <v>91630</v>
+        <v>90233</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10252,25 +10251,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4769</v>
+        <v>5733</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10280,10 +10279,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471431</v>
+        <v>471420</v>
       </c>
       <c r="R87" t="n">
-        <v>7015638</v>
+        <v>7015545</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10324,6 +10323,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -10342,10 +10342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121200484</v>
+        <v>121200486</v>
       </c>
       <c r="B88" t="n">
-        <v>92004</v>
+        <v>90171</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10358,21 +10358,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1968</v>
+        <v>3286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10382,10 +10382,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471377</v>
+        <v>471358</v>
       </c>
       <c r="R88" t="n">
-        <v>7015535</v>
+        <v>7015668</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10444,10 +10444,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200501</v>
+        <v>121200466</v>
       </c>
       <c r="B89" t="n">
-        <v>100347</v>
+        <v>88548</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10456,38 +10456,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>4412</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471381</v>
+        <v>471438</v>
       </c>
       <c r="R89" t="n">
-        <v>7015432</v>
+        <v>7015583</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10546,10 +10546,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200485</v>
+        <v>121200500</v>
       </c>
       <c r="B90" t="n">
-        <v>92004</v>
+        <v>90709</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10562,34 +10562,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471415</v>
+        <v>471425</v>
       </c>
       <c r="R90" t="n">
-        <v>7015546</v>
+        <v>7015607</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10616,12 +10616,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200466</v>
+        <v>121200479</v>
       </c>
       <c r="B91" t="n">
-        <v>88541</v>
+        <v>91977</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4412</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471438</v>
+        <v>471412</v>
       </c>
       <c r="R91" t="n">
-        <v>7015583</v>
+        <v>7015570</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10750,10 +10750,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121200486</v>
+        <v>121200485</v>
       </c>
       <c r="B92" t="n">
-        <v>90163</v>
+        <v>92016</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10766,21 +10766,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3286</v>
+        <v>1968</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10790,10 +10790,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471358</v>
+        <v>471415</v>
       </c>
       <c r="R92" t="n">
-        <v>7015668</v>
+        <v>7015546</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259416</v>
+        <v>121259365</v>
       </c>
       <c r="B93" t="n">
-        <v>57351</v>
+        <v>91977</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,27 +10868,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10896,10 +10895,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471606</v>
+        <v>471356</v>
       </c>
       <c r="R93" t="n">
-        <v>7015715</v>
+        <v>7015390</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10926,17 +10925,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10945,6 +10939,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10963,10 +10958,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259347</v>
+        <v>121259416</v>
       </c>
       <c r="B94" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10979,26 +10974,27 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11006,10 +11002,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471434</v>
+        <v>471606</v>
       </c>
       <c r="R94" t="n">
-        <v>7015412</v>
+        <v>7015715</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11036,12 +11032,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11050,7 +11051,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121259365</v>
+        <v>121259347</v>
       </c>
       <c r="B95" t="n">
-        <v>91965</v>
+        <v>90727</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11085,21 +11085,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11112,10 +11112,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471356</v>
+        <v>471434</v>
       </c>
       <c r="R95" t="n">
-        <v>7015390</v>
+        <v>7015412</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307816</v>
+        <v>121307814</v>
       </c>
       <c r="B96" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,31 +11191,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471234</v>
+        <v>471233</v>
       </c>
       <c r="R96" t="n">
         <v>7015703</v>
@@ -11251,6 +11259,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11280,7 +11293,7 @@
         <v>121307813</v>
       </c>
       <c r="B97" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11379,10 +11392,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307817</v>
+        <v>121307816</v>
       </c>
       <c r="B98" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11419,10 +11432,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471626</v>
+        <v>471234</v>
       </c>
       <c r="R98" t="n">
-        <v>7015589</v>
+        <v>7015703</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11481,10 +11494,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307814</v>
+        <v>121307817</v>
       </c>
       <c r="B99" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11497,42 +11510,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471233</v>
+        <v>471626</v>
       </c>
       <c r="R99" t="n">
-        <v>7015703</v>
+        <v>7015589</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11565,11 +11570,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200475</v>
+        <v>121200484</v>
       </c>
       <c r="B81" t="n">
-        <v>91642</v>
+        <v>92017</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9638,25 +9638,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471431</v>
+        <v>471377</v>
       </c>
       <c r="R81" t="n">
-        <v>7015638</v>
+        <v>7015535</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9728,10 +9728,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200480</v>
+        <v>121200500</v>
       </c>
       <c r="B82" t="n">
-        <v>91977</v>
+        <v>90710</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,34 +9744,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471415</v>
+        <v>471425</v>
       </c>
       <c r="R82" t="n">
-        <v>7015552</v>
+        <v>7015607</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9798,12 +9798,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9830,10 +9830,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121200483</v>
+        <v>121200474</v>
       </c>
       <c r="B83" t="n">
-        <v>90254</v>
+        <v>90234</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9846,21 +9846,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5754</v>
+        <v>5733</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471417</v>
+        <v>471420</v>
       </c>
       <c r="R83" t="n">
-        <v>7015526</v>
+        <v>7015545</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9914,6 +9914,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9932,10 +9933,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121200501</v>
+        <v>121200486</v>
       </c>
       <c r="B84" t="n">
-        <v>100360</v>
+        <v>90172</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9944,38 +9945,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>3286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471381</v>
+        <v>471358</v>
       </c>
       <c r="R84" t="n">
-        <v>7015432</v>
+        <v>7015668</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10002,12 +10003,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10034,10 +10035,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200478</v>
+        <v>121200475</v>
       </c>
       <c r="B85" t="n">
-        <v>86291</v>
+        <v>91643</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10046,25 +10047,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3739</v>
+        <v>4769</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10074,10 +10075,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471414</v>
+        <v>471431</v>
       </c>
       <c r="R85" t="n">
-        <v>7015573</v>
+        <v>7015638</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10118,7 +10119,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10137,10 +10137,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200484</v>
+        <v>121200485</v>
       </c>
       <c r="B86" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471377</v>
+        <v>471415</v>
       </c>
       <c r="R86" t="n">
-        <v>7015535</v>
+        <v>7015546</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10239,10 +10239,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200474</v>
+        <v>121200478</v>
       </c>
       <c r="B87" t="n">
-        <v>90233</v>
+        <v>86291</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10255,21 +10255,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5733</v>
+        <v>3739</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471420</v>
+        <v>471414</v>
       </c>
       <c r="R87" t="n">
-        <v>7015545</v>
+        <v>7015573</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10342,10 +10342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121200486</v>
+        <v>121200480</v>
       </c>
       <c r="B88" t="n">
-        <v>90171</v>
+        <v>91978</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10358,21 +10358,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3286</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10382,10 +10382,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471358</v>
+        <v>471415</v>
       </c>
       <c r="R88" t="n">
-        <v>7015668</v>
+        <v>7015552</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10444,10 +10444,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200466</v>
+        <v>121200501</v>
       </c>
       <c r="B89" t="n">
-        <v>88548</v>
+        <v>100361</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10456,38 +10456,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4412</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471438</v>
+        <v>471381</v>
       </c>
       <c r="R89" t="n">
-        <v>7015583</v>
+        <v>7015432</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10546,10 +10546,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200500</v>
+        <v>121200479</v>
       </c>
       <c r="B90" t="n">
-        <v>90709</v>
+        <v>91978</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10562,34 +10562,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471425</v>
+        <v>471412</v>
       </c>
       <c r="R90" t="n">
-        <v>7015607</v>
+        <v>7015570</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10616,12 +10616,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10648,10 +10648,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200479</v>
+        <v>121200483</v>
       </c>
       <c r="B91" t="n">
-        <v>91977</v>
+        <v>90255</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471412</v>
+        <v>471417</v>
       </c>
       <c r="R91" t="n">
-        <v>7015570</v>
+        <v>7015526</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10750,10 +10750,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121200485</v>
+        <v>121200466</v>
       </c>
       <c r="B92" t="n">
-        <v>92016</v>
+        <v>88548</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10766,21 +10766,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10790,10 +10790,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471415</v>
+        <v>471438</v>
       </c>
       <c r="R92" t="n">
-        <v>7015546</v>
+        <v>7015583</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259365</v>
+        <v>121259347</v>
       </c>
       <c r="B93" t="n">
-        <v>91977</v>
+        <v>90728</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,21 +10868,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10895,10 +10895,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471356</v>
+        <v>471434</v>
       </c>
       <c r="R93" t="n">
-        <v>7015390</v>
+        <v>7015412</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121259347</v>
+        <v>121259365</v>
       </c>
       <c r="B95" t="n">
-        <v>90727</v>
+        <v>91978</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11085,21 +11085,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11112,10 +11112,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471434</v>
+        <v>471356</v>
       </c>
       <c r="R95" t="n">
-        <v>7015412</v>
+        <v>7015390</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307814</v>
+        <v>121307813</v>
       </c>
       <c r="B96" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,42 +11191,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471233</v>
+        <v>471632</v>
       </c>
       <c r="R96" t="n">
-        <v>7015703</v>
+        <v>7015584</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11259,11 +11251,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11290,10 +11277,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307813</v>
+        <v>121307814</v>
       </c>
       <c r="B97" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11306,34 +11293,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471632</v>
+        <v>471233</v>
       </c>
       <c r="R97" t="n">
-        <v>7015584</v>
+        <v>7015703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11366,6 +11361,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11392,10 +11392,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307816</v>
+        <v>121307817</v>
       </c>
       <c r="B98" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471234</v>
+        <v>471626</v>
       </c>
       <c r="R98" t="n">
-        <v>7015703</v>
+        <v>7015589</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11494,10 +11494,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307817</v>
+        <v>121307815</v>
       </c>
       <c r="B99" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11510,34 +11510,50 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471626</v>
+        <v>471653</v>
       </c>
       <c r="R99" t="n">
-        <v>7015589</v>
+        <v>7015676</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11570,6 +11586,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11596,10 +11617,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307815</v>
+        <v>121307816</v>
       </c>
       <c r="B100" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11612,50 +11633,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471653</v>
+        <v>471234</v>
       </c>
       <c r="R100" t="n">
-        <v>7015676</v>
+        <v>7015703</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11688,11 +11693,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200484</v>
+        <v>121200475</v>
       </c>
       <c r="B81" t="n">
-        <v>92017</v>
+        <v>91646</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9638,25 +9638,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471377</v>
+        <v>471431</v>
       </c>
       <c r="R81" t="n">
-        <v>7015535</v>
+        <v>7015638</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9728,10 +9728,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200500</v>
+        <v>121200478</v>
       </c>
       <c r="B82" t="n">
-        <v>90710</v>
+        <v>86294</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,34 +9744,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>3739</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471425</v>
+        <v>471414</v>
       </c>
       <c r="R82" t="n">
-        <v>7015607</v>
+        <v>7015573</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9798,12 +9798,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9812,6 +9812,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9830,10 +9831,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121200474</v>
+        <v>121200485</v>
       </c>
       <c r="B83" t="n">
-        <v>90234</v>
+        <v>92020</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9846,21 +9847,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5733</v>
+        <v>1968</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9870,10 +9871,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471420</v>
+        <v>471415</v>
       </c>
       <c r="R83" t="n">
-        <v>7015545</v>
+        <v>7015546</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9914,7 +9915,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9933,10 +9933,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121200486</v>
+        <v>121200484</v>
       </c>
       <c r="B84" t="n">
-        <v>90172</v>
+        <v>92020</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9949,21 +9949,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3286</v>
+        <v>1968</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9973,10 +9973,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471358</v>
+        <v>471377</v>
       </c>
       <c r="R84" t="n">
-        <v>7015668</v>
+        <v>7015535</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10035,10 +10035,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200475</v>
+        <v>121200501</v>
       </c>
       <c r="B85" t="n">
-        <v>91643</v>
+        <v>100364</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10051,34 +10051,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471431</v>
+        <v>471381</v>
       </c>
       <c r="R85" t="n">
-        <v>7015638</v>
+        <v>7015432</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10105,12 +10105,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10137,10 +10137,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200485</v>
+        <v>121200479</v>
       </c>
       <c r="B86" t="n">
-        <v>92017</v>
+        <v>91981</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10153,21 +10153,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471415</v>
+        <v>471412</v>
       </c>
       <c r="R86" t="n">
-        <v>7015546</v>
+        <v>7015570</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10239,10 +10239,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200478</v>
+        <v>121200500</v>
       </c>
       <c r="B87" t="n">
-        <v>86291</v>
+        <v>90713</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10255,34 +10255,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3739</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471414</v>
+        <v>471425</v>
       </c>
       <c r="R87" t="n">
-        <v>7015573</v>
+        <v>7015607</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10309,12 +10309,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10323,7 +10323,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -10342,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121200480</v>
+        <v>121200483</v>
       </c>
       <c r="B88" t="n">
-        <v>91978</v>
+        <v>90258</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10358,21 +10357,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10382,10 +10381,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471415</v>
+        <v>471417</v>
       </c>
       <c r="R88" t="n">
-        <v>7015552</v>
+        <v>7015526</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10444,10 +10443,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200501</v>
+        <v>121200486</v>
       </c>
       <c r="B89" t="n">
-        <v>100361</v>
+        <v>90175</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10456,38 +10455,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>3286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471381</v>
+        <v>471358</v>
       </c>
       <c r="R89" t="n">
-        <v>7015432</v>
+        <v>7015668</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10514,12 +10513,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10546,10 +10545,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200479</v>
+        <v>121200474</v>
       </c>
       <c r="B90" t="n">
-        <v>91978</v>
+        <v>90237</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10562,21 +10561,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>5733</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10586,10 +10585,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471412</v>
+        <v>471420</v>
       </c>
       <c r="R90" t="n">
-        <v>7015570</v>
+        <v>7015545</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10630,6 +10629,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10648,10 +10648,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200483</v>
+        <v>121200466</v>
       </c>
       <c r="B91" t="n">
-        <v>90255</v>
+        <v>88551</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5754</v>
+        <v>4412</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471417</v>
+        <v>471438</v>
       </c>
       <c r="R91" t="n">
-        <v>7015526</v>
+        <v>7015583</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10750,10 +10750,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121200466</v>
+        <v>121200480</v>
       </c>
       <c r="B92" t="n">
-        <v>88548</v>
+        <v>91981</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10766,21 +10766,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4412</v>
+        <v>4361</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10790,10 +10790,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471438</v>
+        <v>471415</v>
       </c>
       <c r="R92" t="n">
-        <v>7015583</v>
+        <v>7015552</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10855,7 +10855,7 @@
         <v>121259347</v>
       </c>
       <c r="B93" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259416</v>
+        <v>121259365</v>
       </c>
       <c r="B94" t="n">
-        <v>57351</v>
+        <v>91981</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10974,27 +10974,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11002,10 +11001,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471606</v>
+        <v>471356</v>
       </c>
       <c r="R94" t="n">
-        <v>7015715</v>
+        <v>7015390</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11032,17 +11031,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11051,6 +11045,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11069,10 +11064,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121259365</v>
+        <v>121259416</v>
       </c>
       <c r="B95" t="n">
-        <v>91978</v>
+        <v>57354</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11085,26 +11080,27 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11112,10 +11108,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471356</v>
+        <v>471606</v>
       </c>
       <c r="R95" t="n">
-        <v>7015390</v>
+        <v>7015715</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11142,12 +11138,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11156,7 +11157,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307813</v>
+        <v>121307816</v>
       </c>
       <c r="B96" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,21 +11191,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471632</v>
+        <v>471234</v>
       </c>
       <c r="R96" t="n">
-        <v>7015584</v>
+        <v>7015703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11280,7 +11280,7 @@
         <v>121307814</v>
       </c>
       <c r="B97" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>121307817</v>
       </c>
       <c r="B98" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>121307815</v>
       </c>
       <c r="B99" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11617,10 +11617,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307816</v>
+        <v>121307813</v>
       </c>
       <c r="B100" t="n">
-        <v>90728</v>
+        <v>90713</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471234</v>
+        <v>471632</v>
       </c>
       <c r="R100" t="n">
-        <v>7015703</v>
+        <v>7015584</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200475</v>
+        <v>121200478</v>
       </c>
       <c r="B81" t="n">
-        <v>91646</v>
+        <v>86294</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9638,25 +9638,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>3739</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471431</v>
+        <v>471414</v>
       </c>
       <c r="R81" t="n">
-        <v>7015638</v>
+        <v>7015573</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9710,6 +9710,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9728,10 +9729,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200478</v>
+        <v>121200485</v>
       </c>
       <c r="B82" t="n">
-        <v>86294</v>
+        <v>92020</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,21 +9745,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3739</v>
+        <v>1968</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9768,10 +9769,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471414</v>
+        <v>471415</v>
       </c>
       <c r="R82" t="n">
-        <v>7015573</v>
+        <v>7015546</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9812,7 +9813,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9831,10 +9831,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121200485</v>
+        <v>121200479</v>
       </c>
       <c r="B83" t="n">
-        <v>92020</v>
+        <v>91981</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9847,21 +9847,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471415</v>
+        <v>471412</v>
       </c>
       <c r="R83" t="n">
-        <v>7015546</v>
+        <v>7015570</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10035,10 +10035,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200501</v>
+        <v>121200500</v>
       </c>
       <c r="B85" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10047,25 +10047,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471381</v>
+        <v>471425</v>
       </c>
       <c r="R85" t="n">
-        <v>7015432</v>
+        <v>7015607</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10137,10 +10137,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200479</v>
+        <v>121200466</v>
       </c>
       <c r="B86" t="n">
-        <v>91981</v>
+        <v>88551</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10153,21 +10153,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>4412</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471412</v>
+        <v>471438</v>
       </c>
       <c r="R86" t="n">
-        <v>7015570</v>
+        <v>7015583</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10239,10 +10239,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200500</v>
+        <v>121200474</v>
       </c>
       <c r="B87" t="n">
-        <v>90713</v>
+        <v>90237</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10255,34 +10255,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>5733</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471425</v>
+        <v>471420</v>
       </c>
       <c r="R87" t="n">
-        <v>7015607</v>
+        <v>7015545</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10309,12 +10309,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10323,6 +10323,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -10341,10 +10342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121200483</v>
+        <v>121200501</v>
       </c>
       <c r="B88" t="n">
-        <v>90258</v>
+        <v>100364</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10353,38 +10354,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5754</v>
+        <v>222498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471417</v>
+        <v>471381</v>
       </c>
       <c r="R88" t="n">
-        <v>7015526</v>
+        <v>7015432</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10411,12 +10412,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10443,10 +10444,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200486</v>
+        <v>121200475</v>
       </c>
       <c r="B89" t="n">
-        <v>90175</v>
+        <v>91646</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10455,25 +10456,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3286</v>
+        <v>4769</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,10 +10484,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471358</v>
+        <v>471431</v>
       </c>
       <c r="R89" t="n">
-        <v>7015668</v>
+        <v>7015638</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10545,10 +10546,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200474</v>
+        <v>121200483</v>
       </c>
       <c r="B90" t="n">
-        <v>90237</v>
+        <v>90258</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10561,21 +10562,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5733</v>
+        <v>5754</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10585,10 +10586,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471420</v>
+        <v>471417</v>
       </c>
       <c r="R90" t="n">
-        <v>7015545</v>
+        <v>7015526</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10629,7 +10630,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10648,10 +10648,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200466</v>
+        <v>121200486</v>
       </c>
       <c r="B91" t="n">
-        <v>88551</v>
+        <v>90175</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4412</v>
+        <v>3286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471438</v>
+        <v>471358</v>
       </c>
       <c r="R91" t="n">
-        <v>7015583</v>
+        <v>7015668</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259347</v>
+        <v>121259365</v>
       </c>
       <c r="B93" t="n">
-        <v>90731</v>
+        <v>91981</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,21 +10868,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10895,10 +10895,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471434</v>
+        <v>471356</v>
       </c>
       <c r="R93" t="n">
-        <v>7015412</v>
+        <v>7015390</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259365</v>
+        <v>121259347</v>
       </c>
       <c r="B94" t="n">
-        <v>91981</v>
+        <v>90731</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10974,21 +10974,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11001,10 +11001,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471356</v>
+        <v>471434</v>
       </c>
       <c r="R94" t="n">
-        <v>7015390</v>
+        <v>7015412</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307816</v>
+        <v>121307817</v>
       </c>
       <c r="B96" t="n">
         <v>90731</v>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471234</v>
+        <v>471626</v>
       </c>
       <c r="R96" t="n">
-        <v>7015703</v>
+        <v>7015589</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307814</v>
+        <v>121307813</v>
       </c>
       <c r="B97" t="n">
-        <v>57354</v>
+        <v>90713</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11293,42 +11293,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471233</v>
+        <v>471632</v>
       </c>
       <c r="R97" t="n">
-        <v>7015703</v>
+        <v>7015584</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11361,11 +11353,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11392,10 +11379,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307817</v>
+        <v>121307815</v>
       </c>
       <c r="B98" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11408,34 +11395,50 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471626</v>
+        <v>471653</v>
       </c>
       <c r="R98" t="n">
-        <v>7015589</v>
+        <v>7015676</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11468,6 +11471,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11494,7 +11502,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307815</v>
+        <v>121307814</v>
       </c>
       <c r="B99" t="n">
         <v>57354</v>
@@ -11527,20 +11535,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471653</v>
+        <v>471233</v>
       </c>
       <c r="R99" t="n">
-        <v>7015676</v>
+        <v>7015703</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11617,10 +11617,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307813</v>
+        <v>121307816</v>
       </c>
       <c r="B100" t="n">
-        <v>90713</v>
+        <v>90731</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11633,21 +11633,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471632</v>
+        <v>471234</v>
       </c>
       <c r="R100" t="n">
-        <v>7015584</v>
+        <v>7015703</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -10546,10 +10546,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200483</v>
+        <v>121200486</v>
       </c>
       <c r="B90" t="n">
-        <v>90258</v>
+        <v>90175</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10562,21 +10562,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5754</v>
+        <v>3286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471417</v>
+        <v>471358</v>
       </c>
       <c r="R90" t="n">
-        <v>7015526</v>
+        <v>7015668</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10648,10 +10648,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200486</v>
+        <v>121200483</v>
       </c>
       <c r="B91" t="n">
-        <v>90175</v>
+        <v>90258</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3286</v>
+        <v>5754</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471358</v>
+        <v>471417</v>
       </c>
       <c r="R91" t="n">
-        <v>7015668</v>
+        <v>7015526</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200478</v>
+        <v>121200485</v>
       </c>
       <c r="B81" t="n">
-        <v>86294</v>
+        <v>92020</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9642,21 +9642,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3739</v>
+        <v>1968</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471414</v>
+        <v>471415</v>
       </c>
       <c r="R81" t="n">
-        <v>7015573</v>
+        <v>7015546</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9710,7 +9710,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9729,10 +9728,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200485</v>
+        <v>121200478</v>
       </c>
       <c r="B82" t="n">
-        <v>92020</v>
+        <v>86294</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9745,21 +9744,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1968</v>
+        <v>3739</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9769,10 +9768,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471415</v>
+        <v>471414</v>
       </c>
       <c r="R82" t="n">
-        <v>7015546</v>
+        <v>7015573</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9813,6 +9812,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200485</v>
+        <v>121200483</v>
       </c>
       <c r="B81" t="n">
-        <v>92020</v>
+        <v>90264</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9642,21 +9642,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471415</v>
+        <v>471417</v>
       </c>
       <c r="R81" t="n">
-        <v>7015546</v>
+        <v>7015526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9728,10 +9728,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200478</v>
+        <v>121200480</v>
       </c>
       <c r="B82" t="n">
-        <v>86294</v>
+        <v>91987</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,21 +9744,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3739</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471414</v>
+        <v>471415</v>
       </c>
       <c r="R82" t="n">
-        <v>7015573</v>
+        <v>7015552</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9812,7 +9812,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9834,7 +9833,7 @@
         <v>121200479</v>
       </c>
       <c r="B83" t="n">
-        <v>91981</v>
+        <v>91987</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9933,10 +9932,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121200484</v>
+        <v>121200500</v>
       </c>
       <c r="B84" t="n">
-        <v>92020</v>
+        <v>90719</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9949,34 +9948,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471377</v>
+        <v>471425</v>
       </c>
       <c r="R84" t="n">
-        <v>7015535</v>
+        <v>7015607</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10003,12 +10002,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10035,10 +10034,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200500</v>
+        <v>121200466</v>
       </c>
       <c r="B85" t="n">
-        <v>90713</v>
+        <v>88555</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10051,34 +10050,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>4412</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471425</v>
+        <v>471438</v>
       </c>
       <c r="R85" t="n">
-        <v>7015607</v>
+        <v>7015583</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10105,12 +10104,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10137,10 +10136,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200466</v>
+        <v>121200485</v>
       </c>
       <c r="B86" t="n">
-        <v>88551</v>
+        <v>92026</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10153,21 +10152,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10177,10 +10176,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471438</v>
+        <v>471415</v>
       </c>
       <c r="R86" t="n">
-        <v>7015583</v>
+        <v>7015546</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10239,10 +10238,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200474</v>
+        <v>121200478</v>
       </c>
       <c r="B87" t="n">
-        <v>90237</v>
+        <v>86298</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10255,21 +10254,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5733</v>
+        <v>3739</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10279,10 +10278,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471420</v>
+        <v>471414</v>
       </c>
       <c r="R87" t="n">
-        <v>7015545</v>
+        <v>7015573</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10345,7 +10344,7 @@
         <v>121200501</v>
       </c>
       <c r="B88" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10444,10 +10443,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200475</v>
+        <v>121200486</v>
       </c>
       <c r="B89" t="n">
-        <v>91646</v>
+        <v>90181</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10456,25 +10455,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4769</v>
+        <v>3286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10484,10 +10483,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471431</v>
+        <v>471358</v>
       </c>
       <c r="R89" t="n">
-        <v>7015638</v>
+        <v>7015668</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10546,10 +10545,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200486</v>
+        <v>121200484</v>
       </c>
       <c r="B90" t="n">
-        <v>90175</v>
+        <v>92026</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10562,21 +10561,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3286</v>
+        <v>1968</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10586,10 +10585,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471358</v>
+        <v>471377</v>
       </c>
       <c r="R90" t="n">
-        <v>7015668</v>
+        <v>7015535</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10648,10 +10647,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200483</v>
+        <v>121200475</v>
       </c>
       <c r="B91" t="n">
-        <v>90258</v>
+        <v>91652</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10660,25 +10659,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10688,10 +10687,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471417</v>
+        <v>471431</v>
       </c>
       <c r="R91" t="n">
-        <v>7015526</v>
+        <v>7015638</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10750,10 +10749,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121200480</v>
+        <v>121200474</v>
       </c>
       <c r="B92" t="n">
-        <v>91981</v>
+        <v>90243</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10766,21 +10765,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4361</v>
+        <v>5733</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10790,10 +10789,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471415</v>
+        <v>471420</v>
       </c>
       <c r="R92" t="n">
-        <v>7015552</v>
+        <v>7015545</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10834,6 +10833,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259365</v>
+        <v>121259347</v>
       </c>
       <c r="B93" t="n">
-        <v>91981</v>
+        <v>90737</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,21 +10868,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10895,10 +10895,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471356</v>
+        <v>471434</v>
       </c>
       <c r="R93" t="n">
-        <v>7015390</v>
+        <v>7015412</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259347</v>
+        <v>121259365</v>
       </c>
       <c r="B94" t="n">
-        <v>90731</v>
+        <v>91987</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10974,21 +10974,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11001,10 +11001,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471434</v>
+        <v>471356</v>
       </c>
       <c r="R94" t="n">
-        <v>7015412</v>
+        <v>7015390</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11067,7 +11067,7 @@
         <v>121259416</v>
       </c>
       <c r="B95" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307817</v>
+        <v>121307813</v>
       </c>
       <c r="B96" t="n">
-        <v>90731</v>
+        <v>90719</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,21 +11191,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471626</v>
+        <v>471632</v>
       </c>
       <c r="R96" t="n">
-        <v>7015589</v>
+        <v>7015584</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307813</v>
+        <v>121307816</v>
       </c>
       <c r="B97" t="n">
-        <v>90713</v>
+        <v>90737</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11293,21 +11293,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471632</v>
+        <v>471234</v>
       </c>
       <c r="R97" t="n">
-        <v>7015584</v>
+        <v>7015703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11382,7 +11382,7 @@
         <v>121307815</v>
       </c>
       <c r="B98" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>121307814</v>
       </c>
       <c r="B99" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11617,10 +11617,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307816</v>
+        <v>121307817</v>
       </c>
       <c r="B100" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471234</v>
+        <v>471626</v>
       </c>
       <c r="R100" t="n">
-        <v>7015703</v>
+        <v>7015589</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -9626,10 +9626,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200483</v>
+        <v>121200486</v>
       </c>
       <c r="B81" t="n">
-        <v>90264</v>
+        <v>90182</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9642,21 +9642,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5754</v>
+        <v>3286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471417</v>
+        <v>471358</v>
       </c>
       <c r="R81" t="n">
-        <v>7015526</v>
+        <v>7015668</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9728,10 +9728,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200480</v>
+        <v>121200466</v>
       </c>
       <c r="B82" t="n">
-        <v>91987</v>
+        <v>88556</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9744,21 +9744,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>4412</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471415</v>
+        <v>471438</v>
       </c>
       <c r="R82" t="n">
-        <v>7015552</v>
+        <v>7015583</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9830,10 +9830,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121200479</v>
+        <v>121200484</v>
       </c>
       <c r="B83" t="n">
-        <v>91987</v>
+        <v>92027</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9846,21 +9846,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4361</v>
+        <v>1968</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471412</v>
+        <v>471377</v>
       </c>
       <c r="R83" t="n">
-        <v>7015570</v>
+        <v>7015535</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9932,10 +9932,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121200500</v>
+        <v>121200475</v>
       </c>
       <c r="B84" t="n">
-        <v>90719</v>
+        <v>91653</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9944,38 +9944,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471425</v>
+        <v>471431</v>
       </c>
       <c r="R84" t="n">
-        <v>7015607</v>
+        <v>7015638</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10034,10 +10034,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200466</v>
+        <v>121200478</v>
       </c>
       <c r="B85" t="n">
-        <v>88555</v>
+        <v>86299</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10050,21 +10050,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4412</v>
+        <v>3739</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10074,10 +10074,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471438</v>
+        <v>471414</v>
       </c>
       <c r="R85" t="n">
-        <v>7015583</v>
+        <v>7015573</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10118,6 +10118,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10136,10 +10137,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200485</v>
+        <v>121200480</v>
       </c>
       <c r="B86" t="n">
-        <v>92026</v>
+        <v>91988</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10152,21 +10153,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10179,7 +10180,7 @@
         <v>471415</v>
       </c>
       <c r="R86" t="n">
-        <v>7015546</v>
+        <v>7015552</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10238,10 +10239,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200478</v>
+        <v>121200485</v>
       </c>
       <c r="B87" t="n">
-        <v>86298</v>
+        <v>92027</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10254,21 +10255,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3739</v>
+        <v>1968</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10278,10 +10279,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471414</v>
+        <v>471415</v>
       </c>
       <c r="R87" t="n">
-        <v>7015573</v>
+        <v>7015546</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10322,7 +10323,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -10341,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121200501</v>
+        <v>121200483</v>
       </c>
       <c r="B88" t="n">
-        <v>100370</v>
+        <v>90265</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10353,38 +10353,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>5754</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471381</v>
+        <v>471417</v>
       </c>
       <c r="R88" t="n">
-        <v>7015432</v>
+        <v>7015526</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10443,10 +10443,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200486</v>
+        <v>121200474</v>
       </c>
       <c r="B89" t="n">
-        <v>90181</v>
+        <v>90244</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10459,21 +10459,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3286</v>
+        <v>5733</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,10 +10483,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471358</v>
+        <v>471420</v>
       </c>
       <c r="R89" t="n">
-        <v>7015668</v>
+        <v>7015545</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10527,6 +10527,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10545,10 +10546,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200484</v>
+        <v>121200500</v>
       </c>
       <c r="B90" t="n">
-        <v>92026</v>
+        <v>90720</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10561,34 +10562,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471377</v>
+        <v>471425</v>
       </c>
       <c r="R90" t="n">
-        <v>7015535</v>
+        <v>7015607</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10615,12 +10616,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10647,10 +10648,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200475</v>
+        <v>121200501</v>
       </c>
       <c r="B91" t="n">
-        <v>91652</v>
+        <v>100371</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10663,34 +10664,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471431</v>
+        <v>471381</v>
       </c>
       <c r="R91" t="n">
-        <v>7015638</v>
+        <v>7015432</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10717,12 +10718,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10749,10 +10750,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121200474</v>
+        <v>121200479</v>
       </c>
       <c r="B92" t="n">
-        <v>90243</v>
+        <v>91988</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10765,21 +10766,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5733</v>
+        <v>4361</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10789,10 +10790,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471420</v>
+        <v>471412</v>
       </c>
       <c r="R92" t="n">
-        <v>7015545</v>
+        <v>7015570</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10833,7 +10834,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259347</v>
+        <v>121259365</v>
       </c>
       <c r="B93" t="n">
-        <v>90737</v>
+        <v>91988</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,21 +10868,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10895,10 +10895,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471434</v>
+        <v>471356</v>
       </c>
       <c r="R93" t="n">
-        <v>7015412</v>
+        <v>7015390</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259365</v>
+        <v>121259347</v>
       </c>
       <c r="B94" t="n">
-        <v>91987</v>
+        <v>90738</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10974,21 +10974,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11001,10 +11001,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471356</v>
+        <v>471434</v>
       </c>
       <c r="R94" t="n">
-        <v>7015390</v>
+        <v>7015412</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11067,7 +11067,7 @@
         <v>121259416</v>
       </c>
       <c r="B95" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307813</v>
+        <v>121307814</v>
       </c>
       <c r="B96" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,34 +11191,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471632</v>
+        <v>471233</v>
       </c>
       <c r="R96" t="n">
-        <v>7015584</v>
+        <v>7015703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11251,6 +11259,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11277,10 +11290,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307816</v>
+        <v>121307817</v>
       </c>
       <c r="B97" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11317,10 +11330,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471234</v>
+        <v>471626</v>
       </c>
       <c r="R97" t="n">
-        <v>7015703</v>
+        <v>7015589</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11382,7 +11395,7 @@
         <v>121307815</v>
       </c>
       <c r="B98" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11502,10 +11515,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307814</v>
+        <v>121307813</v>
       </c>
       <c r="B99" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11518,42 +11531,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471233</v>
+        <v>471632</v>
       </c>
       <c r="R99" t="n">
-        <v>7015703</v>
+        <v>7015584</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11586,11 +11591,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11617,10 +11617,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307817</v>
+        <v>121307816</v>
       </c>
       <c r="B100" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471626</v>
+        <v>471234</v>
       </c>
       <c r="R100" t="n">
-        <v>7015589</v>
+        <v>7015703</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259365</v>
+        <v>121259347</v>
       </c>
       <c r="B93" t="n">
-        <v>91988</v>
+        <v>90738</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,21 +10868,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10895,10 +10895,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471356</v>
+        <v>471434</v>
       </c>
       <c r="R93" t="n">
-        <v>7015390</v>
+        <v>7015412</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259347</v>
+        <v>121259365</v>
       </c>
       <c r="B94" t="n">
-        <v>90738</v>
+        <v>91988</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10974,21 +10974,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11001,10 +11001,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471434</v>
+        <v>471356</v>
       </c>
       <c r="R94" t="n">
-        <v>7015412</v>
+        <v>7015390</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307814</v>
+        <v>121307817</v>
       </c>
       <c r="B96" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,42 +11191,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471233</v>
+        <v>471626</v>
       </c>
       <c r="R96" t="n">
-        <v>7015703</v>
+        <v>7015589</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11259,11 +11251,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11290,10 +11277,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307817</v>
+        <v>121307813</v>
       </c>
       <c r="B97" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11306,21 +11293,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11330,10 +11317,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471626</v>
+        <v>471632</v>
       </c>
       <c r="R97" t="n">
-        <v>7015589</v>
+        <v>7015584</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11515,10 +11502,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307813</v>
+        <v>121307816</v>
       </c>
       <c r="B99" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11531,21 +11518,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11555,10 +11542,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471632</v>
+        <v>471234</v>
       </c>
       <c r="R99" t="n">
-        <v>7015584</v>
+        <v>7015703</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11617,10 +11604,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307816</v>
+        <v>121307814</v>
       </c>
       <c r="B100" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11633,31 +11620,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471234</v>
+        <v>471233</v>
       </c>
       <c r="R100" t="n">
         <v>7015703</v>
@@ -11693,6 +11688,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259347</v>
+        <v>121259416</v>
       </c>
       <c r="B93" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,26 +10868,27 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10895,10 +10896,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471434</v>
+        <v>471606</v>
       </c>
       <c r="R93" t="n">
-        <v>7015412</v>
+        <v>7015715</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10925,12 +10926,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10939,7 +10945,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11064,10 +11069,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121259416</v>
+        <v>121259347</v>
       </c>
       <c r="B95" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11080,27 +11085,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11108,10 +11112,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471606</v>
+        <v>471434</v>
       </c>
       <c r="R95" t="n">
-        <v>7015715</v>
+        <v>7015412</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11138,17 +11142,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11157,6 +11156,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307817</v>
+        <v>121307813</v>
       </c>
       <c r="B96" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,21 +11191,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471626</v>
+        <v>471632</v>
       </c>
       <c r="R96" t="n">
-        <v>7015589</v>
+        <v>7015584</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307813</v>
+        <v>121307816</v>
       </c>
       <c r="B97" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11293,21 +11293,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471632</v>
+        <v>471234</v>
       </c>
       <c r="R97" t="n">
-        <v>7015584</v>
+        <v>7015703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307815</v>
+        <v>121307814</v>
       </c>
       <c r="B98" t="n">
         <v>57356</v>
@@ -11412,20 +11412,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11435,10 +11427,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471653</v>
+        <v>471233</v>
       </c>
       <c r="R98" t="n">
-        <v>7015676</v>
+        <v>7015703</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11475,7 +11467,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11502,10 +11494,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307816</v>
+        <v>121307815</v>
       </c>
       <c r="B99" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11518,34 +11510,50 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471234</v>
+        <v>471653</v>
       </c>
       <c r="R99" t="n">
-        <v>7015703</v>
+        <v>7015676</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11578,6 +11586,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11604,10 +11617,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307814</v>
+        <v>121307817</v>
       </c>
       <c r="B100" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11620,42 +11633,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471233</v>
+        <v>471626</v>
       </c>
       <c r="R100" t="n">
-        <v>7015703</v>
+        <v>7015589</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11688,11 +11693,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -10963,10 +10963,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259365</v>
+        <v>121259347</v>
       </c>
       <c r="B94" t="n">
-        <v>91988</v>
+        <v>90738</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10979,21 +10979,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471356</v>
+        <v>471434</v>
       </c>
       <c r="R94" t="n">
-        <v>7015390</v>
+        <v>7015412</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121259347</v>
+        <v>121259365</v>
       </c>
       <c r="B95" t="n">
-        <v>90738</v>
+        <v>91988</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11085,21 +11085,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11112,10 +11112,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471434</v>
+        <v>471356</v>
       </c>
       <c r="R95" t="n">
-        <v>7015412</v>
+        <v>7015390</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307814</v>
+        <v>121307815</v>
       </c>
       <c r="B98" t="n">
         <v>57356</v>
@@ -11412,12 +11412,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11427,10 +11435,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471233</v>
+        <v>471653</v>
       </c>
       <c r="R98" t="n">
-        <v>7015703</v>
+        <v>7015676</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11467,7 +11475,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
+          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11494,7 +11502,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307815</v>
+        <v>121307814</v>
       </c>
       <c r="B99" t="n">
         <v>57356</v>
@@ -11527,20 +11535,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471653</v>
+        <v>471233</v>
       </c>
       <c r="R99" t="n">
-        <v>7015676</v>
+        <v>7015703</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -11175,10 +11175,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307813</v>
+        <v>121307814</v>
       </c>
       <c r="B96" t="n">
-        <v>90720</v>
+        <v>57357</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11191,34 +11191,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471632</v>
+        <v>471233</v>
       </c>
       <c r="R96" t="n">
-        <v>7015584</v>
+        <v>7015703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11251,6 +11259,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11280,7 +11293,7 @@
         <v>121307816</v>
       </c>
       <c r="B97" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11379,10 +11392,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307815</v>
+        <v>121307817</v>
       </c>
       <c r="B98" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11395,50 +11408,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471653</v>
+        <v>471626</v>
       </c>
       <c r="R98" t="n">
-        <v>7015676</v>
+        <v>7015589</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11471,11 +11468,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11502,10 +11494,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121307814</v>
+        <v>121307813</v>
       </c>
       <c r="B99" t="n">
-        <v>57356</v>
+        <v>90728</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11518,42 +11510,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471233</v>
+        <v>471632</v>
       </c>
       <c r="R99" t="n">
-        <v>7015703</v>
+        <v>7015584</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11586,11 +11570,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11617,10 +11596,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121307817</v>
+        <v>121307815</v>
       </c>
       <c r="B100" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11633,34 +11612,50 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471626</v>
+        <v>471653</v>
       </c>
       <c r="R100" t="n">
-        <v>7015589</v>
+        <v>7015676</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11693,6 +11688,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78382163</v>
+        <v>101176771</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hamptjärn, i ostsluttning 460 m S om, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471135.4487358893</v>
+        <v>471559</v>
       </c>
       <c r="R2" t="n">
-        <v>7015440.793165267</v>
+        <v>7015733</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kalkgranskog</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,33 +754,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101176776</v>
+        <v>101176772</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471390.6487750282</v>
+        <v>471280</v>
       </c>
       <c r="R3" t="n">
-        <v>7016049.475199182</v>
+        <v>7015669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +863,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101176770</v>
+        <v>101176773</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,42 +881,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471530.9342893704</v>
+        <v>471243</v>
       </c>
       <c r="R4" t="n">
-        <v>7015702.470458556</v>
+        <v>7015717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,24 +938,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,15 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101176795</v>
+        <v>101583034</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471245.8350960497</v>
+        <v>471403</v>
       </c>
       <c r="R5" t="n">
-        <v>7015785.144920524</v>
+        <v>7015511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,22 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,22 +1057,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101176790</v>
+        <v>101583035</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471607.5652026795</v>
+        <v>471474</v>
       </c>
       <c r="R6" t="n">
-        <v>7015496.480680672</v>
+        <v>7015419</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,22 +1129,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,22 +1154,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101176789</v>
+        <v>101672757</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471580.618060883</v>
+        <v>471457</v>
       </c>
       <c r="R7" t="n">
-        <v>7015508.42522586</v>
+        <v>7015640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,22 +1226,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,22 +1251,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101176782</v>
+        <v>101672758</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471420.369375431</v>
+        <v>471457</v>
       </c>
       <c r="R8" t="n">
-        <v>7015690.39328347</v>
+        <v>7015619</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,22 +1323,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,22 +1348,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101176771</v>
+        <v>101583045</v>
       </c>
       <c r="B9" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>492</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1521,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471559.6059147366</v>
+        <v>471481</v>
       </c>
       <c r="R9" t="n">
-        <v>7015732.832783545</v>
+        <v>7015423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,22 +1420,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1434,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1587,22 +1445,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101176785</v>
+        <v>101176749</v>
       </c>
       <c r="B10" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471539.9783955696</v>
+        <v>471298</v>
       </c>
       <c r="R10" t="n">
-        <v>7015705.542127693</v>
+        <v>7015650</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,19 +1520,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,37 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101176800</v>
+        <v>101176750</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1746,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471616.1821200404</v>
+        <v>471280</v>
       </c>
       <c r="R11" t="n">
-        <v>7015604.46582039</v>
+        <v>7015669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,19 +1617,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,15 +1646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101176791</v>
+        <v>101176752</v>
       </c>
       <c r="B12" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,21 +1657,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1858,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471608.1242795571</v>
+        <v>471357</v>
       </c>
       <c r="R12" t="n">
-        <v>7015764.370646585</v>
+        <v>7015697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,22 +1711,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,22 +1736,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101176760</v>
+        <v>101176753</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471558.4511348544</v>
+        <v>471420</v>
       </c>
       <c r="R13" t="n">
-        <v>7015653.151401793</v>
+        <v>7015699</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,19 +1811,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,15 +1840,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101176793</v>
+        <v>101176754</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,21 +1851,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2082,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471486.4226119168</v>
+        <v>471426</v>
       </c>
       <c r="R14" t="n">
-        <v>7015919.869766369</v>
+        <v>7015680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2112,22 +1905,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,22 +1930,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101176753</v>
+        <v>101176755</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471419.9984945306</v>
+        <v>471494</v>
       </c>
       <c r="R15" t="n">
-        <v>7015699.401277074</v>
+        <v>7015715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,19 +2005,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,37 +2034,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101176797</v>
+        <v>101176756</v>
       </c>
       <c r="B16" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2306,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471256.5912509665</v>
+        <v>471610</v>
       </c>
       <c r="R16" t="n">
-        <v>7015676.993550742</v>
+        <v>7015746</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,19 +2102,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,15 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101176763</v>
+        <v>101176758</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471612.8777542982</v>
+        <v>471629</v>
       </c>
       <c r="R17" t="n">
-        <v>7015536.50692253</v>
+        <v>7015728</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,22 +2196,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,22 +2221,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101176752</v>
+        <v>101176759</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471357.303474261</v>
+        <v>471617</v>
       </c>
       <c r="R18" t="n">
-        <v>7015696.356586278</v>
+        <v>7015602</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,19 +2296,9 @@
           <t>2022-05-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,15 +2325,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101176792</v>
+        <v>101176760</v>
       </c>
       <c r="B19" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,21 +2336,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2642,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471603.0745313581</v>
+        <v>471559</v>
       </c>
       <c r="R19" t="n">
-        <v>7015549.650788662</v>
+        <v>7015653</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,22 +2390,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,22 +2415,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101176773</v>
+        <v>101176761</v>
       </c>
       <c r="B20" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,21 +2433,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2754,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471242.9698413348</v>
+        <v>471625</v>
       </c>
       <c r="R20" t="n">
-        <v>7015716.73589812</v>
+        <v>7015566</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,22 +2487,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2819,22 +2512,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101176761</v>
+        <v>101176763</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471624.857397613</v>
+        <v>471613</v>
       </c>
       <c r="R21" t="n">
-        <v>7015565.667865152</v>
+        <v>7015537</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,19 +2587,9 @@
           <t>2022-05-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,15 +2616,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101176784</v>
+        <v>101583016</v>
       </c>
       <c r="B22" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,21 +2627,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2978,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471428.9867831014</v>
+        <v>471362</v>
       </c>
       <c r="R22" t="n">
-        <v>7015696.169853382</v>
+        <v>7015460</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3008,22 +2681,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3043,22 +2706,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101176764</v>
+        <v>101583017</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3066,42 +2724,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471279.490493</v>
+        <v>471341</v>
       </c>
       <c r="R23" t="n">
-        <v>7015666.433692935</v>
+        <v>7015375</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3128,27 +2778,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,22 +2803,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101176758</v>
+        <v>101583018</v>
       </c>
       <c r="B24" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3215,10 +2845,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471628.5398819537</v>
+        <v>471413</v>
       </c>
       <c r="R24" t="n">
-        <v>7015727.722243792</v>
+        <v>7015510</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3245,22 +2875,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3280,22 +2900,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101176749</v>
+        <v>101583019</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3327,10 +2942,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471297.8255022892</v>
+        <v>471432</v>
       </c>
       <c r="R25" t="n">
-        <v>7015649.611277015</v>
+        <v>7015529</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3357,22 +2972,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,22 +2997,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101176796</v>
+        <v>101583020</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,21 +3015,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3439,10 +3039,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471391.429261494</v>
+        <v>471478</v>
       </c>
       <c r="R26" t="n">
-        <v>7015680.745124816</v>
+        <v>7015409</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3469,22 +3069,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3504,22 +3094,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101176786</v>
+        <v>101583021</v>
       </c>
       <c r="B27" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,21 +3112,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3551,10 +3136,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471559.5820518762</v>
+        <v>471478</v>
       </c>
       <c r="R27" t="n">
-        <v>7015730.131616957</v>
+        <v>7015435</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3581,22 +3166,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3616,22 +3191,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101176788</v>
+        <v>101583022</v>
       </c>
       <c r="B28" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3639,21 +3209,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3663,10 +3233,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471617.3212605166</v>
+        <v>471483</v>
       </c>
       <c r="R28" t="n">
-        <v>7015733.674114981</v>
+        <v>7015441</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3693,22 +3263,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3728,44 +3288,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101176767</v>
+        <v>101583023</v>
       </c>
       <c r="B29" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3775,10 +3330,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471621.0737420633</v>
+        <v>471516</v>
       </c>
       <c r="R29" t="n">
-        <v>7015596.768488276</v>
+        <v>7015409</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3805,22 +3360,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3847,15 +3392,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101176756</v>
+        <v>101583026</v>
       </c>
       <c r="B30" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3887,10 +3427,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471610.2115552921</v>
+        <v>471579</v>
       </c>
       <c r="R30" t="n">
-        <v>7015745.442740185</v>
+        <v>7015422</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3917,22 +3457,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,22 +3482,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101176754</v>
+        <v>101672748</v>
       </c>
       <c r="B31" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3999,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471426.1420511624</v>
+        <v>471169</v>
       </c>
       <c r="R31" t="n">
-        <v>7015680.436842354</v>
+        <v>7015463</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,22 +3554,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,22 +3579,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101176794</v>
+        <v>101672749</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4087,21 +3597,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4111,10 +3621,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471268.1429046975</v>
+        <v>471454</v>
       </c>
       <c r="R32" t="n">
-        <v>7015708.406941597</v>
+        <v>7015641</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4141,22 +3651,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,22 +3676,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101176750</v>
+        <v>101672750</v>
       </c>
       <c r="B33" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4223,10 +3718,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471279.5186070397</v>
+        <v>471471</v>
       </c>
       <c r="R33" t="n">
-        <v>7015669.585116525</v>
+        <v>7015612</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4253,22 +3748,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4288,22 +3773,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101176759</v>
+        <v>101672752</v>
       </c>
       <c r="B34" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4335,10 +3815,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471617.067895873</v>
+        <v>471408</v>
       </c>
       <c r="R34" t="n">
-        <v>7015602.657022299</v>
+        <v>7015552</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4365,22 +3845,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4400,44 +3870,39 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101176799</v>
+        <v>101672753</v>
       </c>
       <c r="B35" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4447,10 +3912,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471614.3482020146</v>
+        <v>471384</v>
       </c>
       <c r="R35" t="n">
-        <v>7015754.41080028</v>
+        <v>7015496</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4477,22 +3942,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4512,22 +3967,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101176748</v>
+        <v>104036313</v>
       </c>
       <c r="B36" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4535,34 +3985,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471247.3327186172</v>
+        <v>471262</v>
       </c>
       <c r="R36" t="n">
-        <v>7015750.914418092</v>
+        <v>7016008</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4589,22 +4039,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4624,22 +4064,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>101176772</v>
+        <v>104036314</v>
       </c>
       <c r="B37" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4647,34 +4082,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471279.5186070397</v>
+        <v>471565</v>
       </c>
       <c r="R37" t="n">
-        <v>7015669.585116525</v>
+        <v>7015701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4701,22 +4136,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4736,57 +4161,52 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101176768</v>
+        <v>121200500</v>
       </c>
       <c r="B38" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471606.7606111083</v>
+        <v>471425</v>
       </c>
       <c r="R38" t="n">
-        <v>7015558.623362334</v>
+        <v>7015607</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,22 +4233,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4855,15 +4265,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101583038</v>
+        <v>121307813</v>
       </c>
       <c r="B39" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4871,34 +4276,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471389.5516685403</v>
+        <v>471632</v>
       </c>
       <c r="R39" t="n">
-        <v>7015418.71317733</v>
+        <v>7015584</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4925,22 +4330,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4967,37 +4362,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101583030</v>
+        <v>101176782</v>
       </c>
       <c r="B40" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5007,10 +4397,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471359.7931395941</v>
+        <v>471420</v>
       </c>
       <c r="R40" t="n">
-        <v>7015469.408010216</v>
+        <v>7015690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5037,22 +4427,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5072,26 +4452,21 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101583041</v>
+        <v>101176784</v>
       </c>
       <c r="B41" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5119,10 +4494,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471466.3721004231</v>
+        <v>471429</v>
       </c>
       <c r="R41" t="n">
-        <v>7015437.843441032</v>
+        <v>7015696</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5149,22 +4524,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5184,26 +4549,21 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101583037</v>
+        <v>101176785</v>
       </c>
       <c r="B42" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5231,10 +4591,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471389.4501457299</v>
+        <v>471540</v>
       </c>
       <c r="R42" t="n">
-        <v>7015508.767554495</v>
+        <v>7015706</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5261,22 +4621,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5296,44 +4646,39 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>101583046</v>
+        <v>101176786</v>
       </c>
       <c r="B43" t="n">
-        <v>85689</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>861</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Granulobasidium vellereum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ellis &amp; Cragin) Jülich</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5343,10 +4688,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471477.8389241323</v>
+        <v>471559</v>
       </c>
       <c r="R43" t="n">
-        <v>7015408.924383094</v>
+        <v>7015730</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5373,22 +4718,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5408,44 +4743,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>101583026</v>
+        <v>101176788</v>
       </c>
       <c r="B44" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5455,10 +4785,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471578.5064393729</v>
+        <v>471618</v>
       </c>
       <c r="R44" t="n">
-        <v>7015422.442943174</v>
+        <v>7015734</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5485,22 +4815,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5520,44 +4840,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>101583044</v>
+        <v>101176789</v>
       </c>
       <c r="B45" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5567,10 +4882,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471330.2957758132</v>
+        <v>471580</v>
       </c>
       <c r="R45" t="n">
-        <v>7015448.057662586</v>
+        <v>7015508</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5597,22 +4912,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5632,44 +4937,39 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>101583016</v>
+        <v>101176790</v>
       </c>
       <c r="B46" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5679,10 +4979,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471361.959261617</v>
+        <v>471607</v>
       </c>
       <c r="R46" t="n">
-        <v>7015459.482860535</v>
+        <v>7015497</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5709,22 +5009,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5744,22 +5034,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>101583033</v>
+        <v>101176791</v>
       </c>
       <c r="B47" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5767,21 +5052,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5791,10 +5076,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471463.906431015</v>
+        <v>471608</v>
       </c>
       <c r="R47" t="n">
-        <v>7015464.881426789</v>
+        <v>7015765</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5821,22 +5106,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5863,37 +5138,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>101583019</v>
+        <v>101176792</v>
       </c>
       <c r="B48" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5903,10 +5173,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471432.0168238645</v>
+        <v>471603</v>
       </c>
       <c r="R48" t="n">
-        <v>7015529.551772215</v>
+        <v>7015549</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5933,22 +5203,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5975,19 +5235,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>101583039</v>
+        <v>101583037</v>
       </c>
       <c r="B49" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -6015,10 +5270,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>471426.6374181414</v>
+        <v>471390</v>
       </c>
       <c r="R49" t="n">
-        <v>7015431.441754268</v>
+        <v>7015509</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6048,19 +5303,9 @@
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6087,37 +5332,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>101583027</v>
+        <v>101583038</v>
       </c>
       <c r="B50" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6127,10 +5367,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>471359.7931395941</v>
+        <v>471390</v>
       </c>
       <c r="R50" t="n">
-        <v>7015469.408010216</v>
+        <v>7015419</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6160,19 +5400,9 @@
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6199,19 +5429,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>101583043</v>
+        <v>101583039</v>
       </c>
       <c r="B51" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6239,10 +5464,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>471473.4181496413</v>
+        <v>471426</v>
       </c>
       <c r="R51" t="n">
-        <v>7015418.869577772</v>
+        <v>7015431</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6272,19 +5497,9 @@
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6311,19 +5526,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>101583042</v>
+        <v>101583041</v>
       </c>
       <c r="B52" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6351,10 +5561,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>471472.5523484572</v>
+        <v>471466</v>
       </c>
       <c r="R52" t="n">
-        <v>7015422.929706904</v>
+        <v>7015438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6384,19 +5594,9 @@
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6423,37 +5623,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>101583023</v>
+        <v>101583042</v>
       </c>
       <c r="B53" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6463,10 +5658,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471516.6202902102</v>
+        <v>471473</v>
       </c>
       <c r="R53" t="n">
-        <v>7015409.481618867</v>
+        <v>7015423</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6496,19 +5691,9 @@
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6535,15 +5720,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>101583045</v>
+        <v>101583043</v>
       </c>
       <c r="B54" t="n">
-        <v>90052</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6551,21 +5731,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6575,10 +5755,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471481.5693787539</v>
+        <v>471474</v>
       </c>
       <c r="R54" t="n">
-        <v>7015422.849826377</v>
+        <v>7015419</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6608,19 +5788,9 @@
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6647,37 +5817,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>101583017</v>
+        <v>101672759</v>
       </c>
       <c r="B55" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6687,10 +5852,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>471341.3726153788</v>
+        <v>471447</v>
       </c>
       <c r="R55" t="n">
-        <v>7015375.464810573</v>
+        <v>7015619</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6717,22 +5882,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6759,15 +5914,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101583018</v>
+        <v>101583033</v>
       </c>
       <c r="B56" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6775,21 +5925,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6799,10 +5949,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>471412.4589522399</v>
+        <v>471464</v>
       </c>
       <c r="R56" t="n">
-        <v>7015510.36421595</v>
+        <v>7015465</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6832,19 +5982,9 @@
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6871,15 +6011,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>101583020</v>
+        <v>121200484</v>
       </c>
       <c r="B57" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6887,34 +6022,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>1968</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471477.8389241323</v>
+        <v>471377</v>
       </c>
       <c r="R57" t="n">
-        <v>7015408.924383094</v>
+        <v>7015535</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6941,22 +6076,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6983,50 +6108,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>101583031</v>
+        <v>121200485</v>
       </c>
       <c r="B58" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>1968</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>471434.5101321503</v>
+        <v>471415</v>
       </c>
       <c r="R58" t="n">
-        <v>7015505.665883353</v>
+        <v>7015546</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7053,22 +6173,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7095,15 +6205,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>101583021</v>
+        <v>121200486</v>
       </c>
       <c r="B59" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7111,34 +6216,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>3286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>471478.5211047184</v>
+        <v>471358</v>
       </c>
       <c r="R59" t="n">
-        <v>7015435.034171135</v>
+        <v>7015668</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7165,22 +6270,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7207,15 +6302,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>101583022</v>
+        <v>121200478</v>
       </c>
       <c r="B60" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7223,34 +6313,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>3739</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>471483.0854314212</v>
+        <v>471414</v>
       </c>
       <c r="R60" t="n">
-        <v>7015441.297531115</v>
+        <v>7015573</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7277,30 +6367,21 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7319,15 +6400,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>101583034</v>
+        <v>73777410</v>
       </c>
       <c r="B61" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7335,37 +6411,51 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Namnlös, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471403.4461655095</v>
+        <v>471295</v>
       </c>
       <c r="R61" t="n">
-        <v>7015510.894515856</v>
+        <v>7015809</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7389,22 +6479,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7413,33 +6493,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anders Forsgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Anders Forsgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>101583035</v>
+        <v>121200479</v>
       </c>
       <c r="B62" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7447,34 +6523,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>4361</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471473.4181496413</v>
+        <v>471412</v>
       </c>
       <c r="R62" t="n">
-        <v>7015418.869577772</v>
+        <v>7015570</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7501,22 +6577,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7543,15 +6609,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>101583032</v>
+        <v>121200480</v>
       </c>
       <c r="B63" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7559,42 +6620,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471394.3853794024</v>
+        <v>471415</v>
       </c>
       <c r="R63" t="n">
-        <v>7015506.022134358</v>
+        <v>7015552</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7621,22 +6674,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,15 +6706,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>101672757</v>
+        <v>121259365</v>
       </c>
       <c r="B64" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7679,34 +6717,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471456.8890881174</v>
+        <v>471356</v>
       </c>
       <c r="R64" t="n">
-        <v>7015639.642507147</v>
+        <v>7015390</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7733,22 +6774,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7757,6 +6788,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7775,15 +6807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>101672755</v>
+        <v>121200466</v>
       </c>
       <c r="B65" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7791,42 +6818,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471143.2584411444</v>
+        <v>471438</v>
       </c>
       <c r="R65" t="n">
-        <v>7015456.932885901</v>
+        <v>7015583</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7853,27 +6872,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7900,50 +6904,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>101672758</v>
+        <v>121200475</v>
       </c>
       <c r="B66" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471457.1523123895</v>
+        <v>471431</v>
       </c>
       <c r="R66" t="n">
-        <v>7015618.478699169</v>
+        <v>7015638</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7970,22 +6969,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8012,15 +7001,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>101672756</v>
+        <v>121200474</v>
       </c>
       <c r="B67" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91424</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8028,42 +7012,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>5733</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471448.4472586885</v>
+        <v>471420</v>
       </c>
       <c r="R67" t="n">
-        <v>7015653.674854988</v>
+        <v>7015545</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8090,35 +7066,21 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8137,15 +7099,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>101672750</v>
+        <v>121200483</v>
       </c>
       <c r="B68" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8153,34 +7110,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>5754</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Trusta - Rödön, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471471.0720079607</v>
+        <v>471417</v>
       </c>
       <c r="R68" t="n">
-        <v>7015612.051876908</v>
+        <v>7015526</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,22 +7164,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8249,37 +7196,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>101672749</v>
+        <v>101176794</v>
       </c>
       <c r="B69" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8289,10 +7231,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471453.7413237786</v>
+        <v>471268</v>
       </c>
       <c r="R69" t="n">
-        <v>7015640.57090154</v>
+        <v>7015708</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8319,22 +7261,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8354,44 +7286,39 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>101672754</v>
+        <v>101176795</v>
       </c>
       <c r="B70" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8401,10 +7328,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471373.8453937669</v>
+        <v>471246</v>
       </c>
       <c r="R70" t="n">
-        <v>7015477.838094932</v>
+        <v>7015785</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8431,22 +7358,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8466,44 +7383,39 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>101672753</v>
+        <v>101176796</v>
       </c>
       <c r="B71" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8513,10 +7425,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471383.4731829972</v>
+        <v>471391</v>
       </c>
       <c r="R71" t="n">
-        <v>7015495.763075004</v>
+        <v>7015681</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8543,22 +7455,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8578,22 +7480,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>101672752</v>
+        <v>101176748</v>
       </c>
       <c r="B72" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8601,21 +7498,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8625,10 +7522,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471407.8715641362</v>
+        <v>471248</v>
       </c>
       <c r="R72" t="n">
-        <v>7015552.278936082</v>
+        <v>7015751</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8655,22 +7552,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8690,22 +7577,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>101672759</v>
+        <v>101176776</v>
       </c>
       <c r="B73" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8713,21 +7595,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8737,10 +7619,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471447.2341815716</v>
+        <v>471390</v>
       </c>
       <c r="R73" t="n">
-        <v>7015618.566645715</v>
+        <v>7016050</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8767,22 +7649,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8809,15 +7681,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>101672747</v>
+        <v>101176767</v>
       </c>
       <c r="B74" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8825,21 +7692,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221235</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8849,10 +7716,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471172.7569835929</v>
+        <v>471621</v>
       </c>
       <c r="R74" t="n">
-        <v>7015478.281474361</v>
+        <v>7015597</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8879,22 +7746,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8921,37 +7778,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>101672748</v>
+        <v>101176768</v>
       </c>
       <c r="B75" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8961,10 +7813,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471169.0131560004</v>
+        <v>471607</v>
       </c>
       <c r="R75" t="n">
-        <v>7015463.005918111</v>
+        <v>7015558</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8991,22 +7843,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9033,66 +7875,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102814302</v>
+        <v>101583029</v>
       </c>
       <c r="B76" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471585.220333708</v>
+        <v>471609</v>
       </c>
       <c r="R76" t="n">
-        <v>7015672.275305551</v>
+        <v>7015404</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9119,22 +7940,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9143,7 +7954,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9162,50 +7972,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>104036313</v>
+        <v>101176770</v>
       </c>
       <c r="B77" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471262.2541063273</v>
+        <v>471531</v>
       </c>
       <c r="R77" t="n">
-        <v>7016008.301162178</v>
+        <v>7015703</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9232,22 +8045,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9267,57 +8075,60 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104036314</v>
+        <v>101583032</v>
       </c>
       <c r="B78" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471565.1840999595</v>
+        <v>471395</v>
       </c>
       <c r="R78" t="n">
-        <v>7015700.817065686</v>
+        <v>7015506</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9344,22 +8155,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9386,50 +8187,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>104036322</v>
+        <v>101672755</v>
       </c>
       <c r="B79" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471398.4583248426</v>
+        <v>471143</v>
       </c>
       <c r="R79" t="n">
-        <v>7015659.971696866</v>
+        <v>7015457</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9456,22 +8260,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9498,32 +8297,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>106114385</v>
+        <v>101672756</v>
       </c>
       <c r="B80" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9531,20 +8325,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9554,10 +8340,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471384.4429403709</v>
+        <v>471449</v>
       </c>
       <c r="R80" t="n">
-        <v>7015655.593838001</v>
+        <v>7015653</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9584,22 +8370,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9614,7 +8395,7 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -9626,15 +8407,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121200486</v>
+        <v>101176764</v>
       </c>
       <c r="B81" t="n">
-        <v>90182</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9642,34 +8418,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3286</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471358</v>
+        <v>471280</v>
       </c>
       <c r="R81" t="n">
-        <v>7015668</v>
+        <v>7015666</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9696,12 +8480,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9721,22 +8510,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121200466</v>
+        <v>106114385</v>
       </c>
       <c r="B82" t="n">
-        <v>88556</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9744,34 +8528,50 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471438</v>
+        <v>471385</v>
       </c>
       <c r="R82" t="n">
-        <v>7015583</v>
+        <v>7015656</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9798,12 +8598,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9818,7 +8618,7 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -9830,15 +8630,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121200484</v>
+        <v>121259416</v>
       </c>
       <c r="B83" t="n">
-        <v>92027</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9846,34 +8641,38 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1968</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471377</v>
+        <v>471606</v>
       </c>
       <c r="R83" t="n">
-        <v>7015535</v>
+        <v>7015715</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9900,12 +8699,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9932,50 +8736,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121200475</v>
+        <v>121307814</v>
       </c>
       <c r="B84" t="n">
-        <v>91653</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471431</v>
+        <v>471233</v>
       </c>
       <c r="R84" t="n">
-        <v>7015638</v>
+        <v>7015703</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10002,12 +8809,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10034,15 +8846,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121200478</v>
+        <v>121307815</v>
       </c>
       <c r="B85" t="n">
-        <v>86299</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10050,34 +8857,50 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3739</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Hamptjärnen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471414</v>
+        <v>471653</v>
       </c>
       <c r="R85" t="n">
-        <v>7015573</v>
+        <v>7015676</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10104,21 +8927,25 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF85" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10137,50 +8964,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121200480</v>
+        <v>101583027</v>
       </c>
       <c r="B86" t="n">
-        <v>91988</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>219847</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471415</v>
+        <v>471360</v>
       </c>
       <c r="R86" t="n">
-        <v>7015552</v>
+        <v>7015470</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10207,12 +9029,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10239,50 +9061,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121200485</v>
+        <v>101583028</v>
       </c>
       <c r="B87" t="n">
-        <v>92027</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1968</v>
+        <v>219847</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471415</v>
+        <v>471442</v>
       </c>
       <c r="R87" t="n">
-        <v>7015546</v>
+        <v>7015501</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10309,12 +9126,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10341,50 +9158,61 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121200483</v>
+        <v>102814302</v>
       </c>
       <c r="B88" t="n">
-        <v>90265</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471417</v>
+        <v>471585</v>
       </c>
       <c r="R88" t="n">
-        <v>7015526</v>
+        <v>7015672</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10411,12 +9239,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10425,6 +9253,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10443,37 +9272,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121200474</v>
+        <v>104036322</v>
       </c>
       <c r="B89" t="n">
-        <v>90244</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5733</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,10 +9307,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471420</v>
+        <v>471399</v>
       </c>
       <c r="R89" t="n">
-        <v>7015545</v>
+        <v>7015660</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10513,21 +9337,20 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF89" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10546,15 +9369,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121200500</v>
+        <v>78382163</v>
       </c>
       <c r="B90" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10562,37 +9380,41 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Hamptjärn, i ostsluttning 460 m S om, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471425</v>
+        <v>471135</v>
       </c>
       <c r="R90" t="n">
-        <v>7015607</v>
+        <v>7015441</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10616,12 +9438,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Kalkgranskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10636,62 +9463,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121200501</v>
+        <v>101672747</v>
       </c>
       <c r="B91" t="n">
-        <v>100371</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hamptjärnen Ö, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471381</v>
+        <v>471173</v>
       </c>
       <c r="R91" t="n">
-        <v>7015432</v>
+        <v>7015478</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10718,12 +9540,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10750,50 +9572,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121200479</v>
+        <v>101583030</v>
       </c>
       <c r="B92" t="n">
-        <v>91988</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4361</v>
+        <v>221952</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471412</v>
+        <v>471360</v>
       </c>
       <c r="R92" t="n">
-        <v>7015570</v>
+        <v>7015470</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10820,12 +9637,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10852,54 +9669,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121259416</v>
+        <v>101583031</v>
       </c>
       <c r="B93" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471606</v>
+        <v>471434</v>
       </c>
       <c r="R93" t="n">
-        <v>7015715</v>
+        <v>7015505</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10926,17 +9734,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10963,53 +9766,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121259347</v>
+        <v>101672754</v>
       </c>
       <c r="B94" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471434</v>
+        <v>471374</v>
       </c>
       <c r="R94" t="n">
-        <v>7015412</v>
+        <v>7015478</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11036,12 +9831,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11050,7 +9845,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11069,53 +9863,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121259365</v>
+        <v>101176797</v>
       </c>
       <c r="B95" t="n">
-        <v>91988</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471356</v>
+        <v>471256</v>
       </c>
       <c r="R95" t="n">
-        <v>7015390</v>
+        <v>7015677</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11142,12 +9928,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11156,7 +9942,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11168,65 +9953,52 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121307814</v>
+        <v>101176799</v>
       </c>
       <c r="B96" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Hamptjärnen SÖ, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471233</v>
+        <v>471614</v>
       </c>
       <c r="R96" t="n">
-        <v>7015703</v>
+        <v>7015755</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11253,17 +10025,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Sannolikt ett gammalt tretå-bohål i en granhögstubbe med grantickor, ca 1,5m m ovan mark.</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11283,57 +10050,52 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121307816</v>
+        <v>101176800</v>
       </c>
       <c r="B97" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hamptjärnen SÖ, Jmt</t>
+          <t>Trusta - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471234</v>
+        <v>471616</v>
       </c>
       <c r="R97" t="n">
-        <v>7015703</v>
+        <v>7015605</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11360,12 +10122,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11385,57 +10147,52 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121307817</v>
+        <v>121200501</v>
       </c>
       <c r="B98" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Hamptjärnen SÖ, Jmt</t>
+          <t>Hamptjärnen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471626</v>
+        <v>471381</v>
       </c>
       <c r="R98" t="n">
-        <v>7015589</v>
+        <v>7015432</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11462,12 +10219,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11491,231 +10248,6 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>121307813</v>
-      </c>
-      <c r="B99" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Hamptjärnen SÖ, Jmt</t>
-        </is>
-      </c>
-      <c r="Q99" t="n">
-        <v>471632</v>
-      </c>
-      <c r="R99" t="n">
-        <v>7015584</v>
-      </c>
-      <c r="S99" t="n">
-        <v>10</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AD99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT99" t="inlineStr"/>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>121307815</v>
-      </c>
-      <c r="B100" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Hamptjärnen SÖ, Jmt</t>
-        </is>
-      </c>
-      <c r="Q100" t="n">
-        <v>471653</v>
-      </c>
-      <c r="R100" t="n">
-        <v>7015676</v>
-      </c>
-      <c r="S100" t="n">
-        <v>10</v>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Födosökande på både stam och grenar, högt upp i en lite grövre gran.</t>
-        </is>
-      </c>
-      <c r="AD100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT100" t="inlineStr"/>
-      <c r="AW100" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51148-2024 artfynd.xlsx
+++ b/artfynd/A 51148-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176771</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176772</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176773</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583034</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583035</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672757</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672758</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583045</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176749</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176750</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176752</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176753</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176754</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176755</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176756</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176758</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176759</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176760</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2516,6 +2611,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176761</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2613,6 +2713,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176763</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583016</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583017</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2904,6 +3019,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583018</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3001,6 +3121,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583019</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3098,6 +3223,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583020</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3195,6 +3325,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583021</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3292,6 +3427,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583022</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3389,6 +3529,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583023</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3486,6 +3631,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583026</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3583,6 +3733,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672748</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3680,6 +3835,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672749</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3777,6 +3937,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672750</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3874,6 +4039,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672752</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3971,6 +4141,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672753</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4068,6 +4243,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036313</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4165,6 +4345,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036314</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4262,6 +4447,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200500</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4359,6 +4549,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121307813</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4456,6 +4651,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176782</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4553,6 +4753,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176784</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4650,6 +4855,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176785</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4747,6 +4957,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176786</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4844,6 +5059,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176788</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4941,6 +5161,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176789</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5038,6 +5263,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176790</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5135,6 +5365,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176791</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5232,6 +5467,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176792</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5329,6 +5569,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583037</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5426,6 +5671,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583038</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5523,6 +5773,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583039</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5620,6 +5875,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583041</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5717,6 +5977,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583042</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5814,6 +6079,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583043</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5911,6 +6181,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672759</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6008,6 +6283,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583033</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6105,6 +6385,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200484</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6202,6 +6487,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200485</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6299,6 +6589,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200486</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6397,6 +6692,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200478</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6509,6 +6809,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777410</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6606,6 +6911,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200479</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6703,6 +7013,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200480</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6804,6 +7119,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121259365</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6901,6 +7221,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200466</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6998,6 +7323,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200475</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7096,6 +7426,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200474</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7193,6 +7528,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200483</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7290,6 +7630,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176794</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7387,6 +7732,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176795</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7484,6 +7834,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176796</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7581,6 +7936,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176748</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7678,6 +8038,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176776</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7775,6 +8140,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176767</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7872,6 +8242,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176768</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7969,6 +8344,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583029</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8079,6 +8459,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176770</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8184,6 +8569,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583032</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8294,6 +8684,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672755</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8404,6 +8799,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672756</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8514,6 +8914,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176764</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8627,6 +9032,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106114385</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8733,6 +9143,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121259416</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8843,6 +9258,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121307814</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8961,6 +9381,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121307815</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9058,6 +9483,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583027</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9155,6 +9585,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583028</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9269,6 +9704,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102814302</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9366,6 +9806,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036322</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9472,6 +9917,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78382163</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9569,6 +10019,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672747</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9666,6 +10121,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583030</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9763,6 +10223,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101583031</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9860,6 +10325,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101672754</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9957,6 +10427,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176797</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10054,6 +10529,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176799</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10151,6 +10631,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101176800</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10248,8 +10733,112 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200501</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>